--- a/Costes PREP.xlsx
+++ b/Costes PREP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philip\Documents\GitHub\Lenaca-PrEP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\PrEP-LEN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3C72A9-881C-4AA6-B9E8-DDBC48B198D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003186D1-0F52-4DCB-BF60-E08EF87ED782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12150" yWindow="1560" windowWidth="25230" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2670" yWindow="3375" windowWidth="16290" windowHeight="16650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -572,8 +572,8 @@
         <v>14</v>
       </c>
       <c r="B2" s="2">
-        <f>187.39/30</f>
-        <v>6.2463333333333333</v>
+        <f>187.39/28</f>
+        <v>6.6924999999999999</v>
       </c>
       <c r="C2" s="2">
         <f>0.97</f>
@@ -708,15 +708,15 @@
         <v>92.92</v>
       </c>
       <c r="D6" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="0"/>
-        <v>1.7869230769230771</v>
+        <v>7.1476923076923082</v>
       </c>
       <c r="F6" s="2">
         <f t="shared" si="1"/>
-        <v>1.7869230769230771</v>
+        <v>7.1476923076923082</v>
       </c>
       <c r="G6" s="2"/>
       <c r="I6" t="s">
@@ -743,18 +743,18 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
-        <v>90.92</v>
+        <v>13.53</v>
       </c>
       <c r="D7" s="2">
         <v>4</v>
       </c>
       <c r="E7" s="2">
         <f t="shared" si="0"/>
-        <v>6.993846153846154</v>
+        <v>1.0407692307692307</v>
       </c>
       <c r="F7" s="2">
         <f t="shared" si="1"/>
-        <v>6.993846153846154</v>
+        <v>1.0407692307692307</v>
       </c>
       <c r="G7" s="2"/>
     </row>
@@ -821,18 +821,18 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2">
-        <v>4.34</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="D10" s="2">
         <v>4</v>
       </c>
       <c r="E10" s="2">
         <f t="shared" si="0"/>
-        <v>0.33384615384615385</v>
+        <v>0.33846153846153848</v>
       </c>
       <c r="F10" s="2">
         <f t="shared" ref="F10:F17" si="2">(C10*D10)/52</f>
-        <v>0.33384615384615385</v>
+        <v>0.33846153846153848</v>
       </c>
       <c r="G10" s="2"/>
     </row>
@@ -842,18 +842,18 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="D11" s="2">
         <v>4</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="0"/>
-        <v>0.23538461538461539</v>
+        <v>0.23846153846153847</v>
       </c>
       <c r="F11" s="2">
         <f t="shared" si="2"/>
-        <v>0.23538461538461539</v>
+        <v>0.23846153846153847</v>
       </c>
       <c r="G11" s="2"/>
       <c r="L11">
@@ -892,18 +892,18 @@
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="D13" s="2">
         <v>4</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>5.4615384615384614E-2</v>
+        <v>5.6153846153846151E-2</v>
       </c>
       <c r="F13" s="2">
         <f t="shared" si="2"/>
-        <v>5.4615384615384614E-2</v>
+        <v>5.6153846153846151E-2</v>
       </c>
       <c r="G13" s="2"/>
     </row>
@@ -913,18 +913,18 @@
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="D14" s="2">
         <v>4</v>
       </c>
       <c r="E14" s="2">
         <f t="shared" si="0"/>
-        <v>5.4615384615384614E-2</v>
+        <v>5.5384615384615379E-2</v>
       </c>
       <c r="F14" s="2">
         <f t="shared" si="2"/>
-        <v>5.4615384615384614E-2</v>
+        <v>5.5384615384615379E-2</v>
       </c>
       <c r="G14" s="2"/>
     </row>
@@ -934,18 +934,18 @@
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2">
         <v>4</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="0"/>
-        <v>0.30153846153846153</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="F15" s="2">
         <f t="shared" si="2"/>
-        <v>0.30153846153846153</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="G15" s="2"/>
     </row>
@@ -955,18 +955,18 @@
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2">
-        <v>4.3099999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="D16" s="2">
         <v>4</v>
       </c>
       <c r="E16" s="2">
         <f t="shared" si="0"/>
-        <v>0.3315384615384615</v>
+        <v>0.33846153846153848</v>
       </c>
       <c r="F16" s="2">
         <f t="shared" si="2"/>
-        <v>0.3315384615384615</v>
+        <v>0.33846153846153848</v>
       </c>
       <c r="G16" s="2"/>
     </row>
@@ -1018,11 +1018,11 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2">
         <f>E3+E4+E5+E6+E7+E8+E9+E10+E11+E12+E13+E14+E15+E16+E17+E18</f>
-        <v>23.231730769230772</v>
+        <v>22.662500000000001</v>
       </c>
       <c r="F19" s="2">
         <f>F3+F4+F5+F6+F7+F8+F9+F10+F11+F12+F13+F14+F15+F16+F17+F18</f>
-        <v>24.270192307692312</v>
+        <v>23.700961538461542</v>
       </c>
       <c r="G19" s="2"/>
       <c r="K19">
@@ -1041,11 +1041,11 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2">
         <f>E2+E5+E6+E8+E7+E9+E10+E11+E12+E13+E14+E15+E16+E17</f>
-        <v>26.949038461538457</v>
+        <v>26.379807692307693</v>
       </c>
       <c r="F20" s="2">
         <f>F2+F5+F6+F8+F7+F9+F10+F11+F12+F13+F14+F15+F16+F17</f>
-        <v>898.82788461538462</v>
+        <v>898.25865384615361</v>
       </c>
       <c r="G20" s="2"/>
     </row>
@@ -1060,11 +1060,11 @@
       <c r="D21" s="2"/>
       <c r="E21" s="2">
         <f>E2+E3+E4+E7+E8+E9+E10+E11+E12+E13+E14+E15+E16</f>
-        <v>18.824615384615381</v>
+        <v>12.894615384615385</v>
       </c>
       <c r="F21" s="2">
         <f>F2+F3+F4+F7+F8+F9+F10+F11+F12+F13+F14+F15+F16</f>
-        <v>890.70346153846162</v>
+        <v>884.77346153846145</v>
       </c>
       <c r="G21" s="2"/>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="F23">
         <f>117-(F20-F2)</f>
-        <v>96.859615384615381</v>
+        <v>97.428846153846393</v>
       </c>
       <c r="G23">
         <f>158-(G20-G2)</f>
@@ -1172,6 +1172,10 @@
         <f t="shared" si="3"/>
         <v>3.7234615384615384</v>
       </c>
+      <c r="G28">
+        <f>120.85*2/52</f>
+        <v>4.648076923076923</v>
+      </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
@@ -1207,8 +1211,12 @@
         <v>1</v>
       </c>
       <c r="E30" s="4">
-        <f t="shared" si="3"/>
+        <f>C30*D30/52</f>
         <v>8.2219230769230762</v>
+      </c>
+      <c r="H30">
+        <f>E10+E11+E12+E13+E14+E15+E16</f>
+        <v>1.3923076923076922</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1227,7 +1235,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="4">
-        <f t="shared" si="3"/>
+        <f>C31*D31/52</f>
         <v>2.9038461538461537</v>
       </c>
     </row>
@@ -1250,7 +1258,7 @@
         <v>0.33384615384615385</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>31</v>
       </c>
@@ -1268,8 +1276,12 @@
         <f t="shared" si="3"/>
         <v>0.23538461538461539</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <f>E32+E33+E35+E34+E36+E37</f>
+        <v>1.0376923076923077</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>3</v>
       </c>
@@ -1288,7 +1300,7 @@
         <v>5.7692307692307696E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>4</v>
       </c>
@@ -1307,7 +1319,7 @@
         <v>5.4615384615384614E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>5</v>
       </c>
@@ -1326,7 +1338,7 @@
         <v>5.4615384615384614E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>6</v>
       </c>
@@ -1345,7 +1357,7 @@
         <v>0.30153846153846153</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1355,14 +1367,14 @@
         <v>188.54730769230773</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
